--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013B2060-0B57-45C7-BD6B-12E9A23CB809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B9845-AB3B-4DCD-A637-74907948302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -341,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,6 +524,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +734,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -742,6 +748,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1254,7 +1261,7 @@
       <c r="E5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="1"/>

--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B9845-AB3B-4DCD-A637-74907948302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E1DF13-F6AD-4750-A968-24BFB770F741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>1111</t>
   </si>
   <si>
-    <t>1234567891</t>
-  </si>
-  <si>
     <t>Navigate to Login page</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
   </si>
   <si>
     <t>01_CompanyLogin</t>
+  </si>
+  <si>
+    <t>9527812704</t>
   </si>
 </sst>
 </file>
@@ -1173,21 +1173,21 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>5</v>
@@ -1198,21 +1198,21 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>5</v>
@@ -1223,23 +1223,23 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>5</v>
@@ -1250,23 +1250,23 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>5</v>
@@ -1277,21 +1277,21 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>5</v>
@@ -1302,23 +1302,23 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>5</v>
@@ -1329,21 +1329,21 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>5</v>
@@ -1354,23 +1354,23 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E1DF13-F6AD-4750-A968-24BFB770F741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA3AFC7-4325-4200-A189-B18D1E5A5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>MODULE_NAME</t>
   </si>
   <si>
-    <t>2601000018</t>
-  </si>
-  <si>
     <t>Login_01</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
   </si>
   <si>
     <t>9527812704</t>
+  </si>
+  <si>
+    <t>2602000005</t>
   </si>
 </sst>
 </file>
@@ -734,7 +734,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -749,6 +749,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1156,10 +1159,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>2</v>
@@ -1169,208 +1172,208 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
+      <c r="A3" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
+      <c r="A4" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
+      <c r="A5" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
+      <c r="A6" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
+      <c r="A7" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
+      <c r="A8" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/02_InfluencerLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA3AFC7-4325-4200-A189-B18D1E5A5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83382B6B-C740-4213-AAA1-1FE2F9ED23DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -173,20 +173,21 @@
     <t>1234568</t>
   </si>
   <si>
-    <t>selectenglishlanguage
+    <t>01_CompanyLogin</t>
+  </si>
+  <si>
+    <t>9527812704</t>
+  </si>
+  <si>
+    <t>2602000005</t>
+  </si>
+  <si>
+    <t>relaunchapp
+selectenglishlanguage
 refreshloginpage
 clickonselectlanguagesubmitbtn
 clickondeclarationnextbtn
 verifyentermobilenofielddisplay</t>
-  </si>
-  <si>
-    <t>01_CompanyLogin</t>
-  </si>
-  <si>
-    <t>9527812704</t>
-  </si>
-  <si>
-    <t>2602000005</t>
   </si>
 </sst>
 </file>
@@ -1171,12 +1172,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1185,7 +1186,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -1198,10 +1199,10 @@
     </row>
     <row r="3" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1223,10 +1224,10 @@
     </row>
     <row r="4" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>27</v>
@@ -1250,10 +1251,10 @@
     </row>
     <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -1265,7 +1266,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
@@ -1277,10 +1278,10 @@
     </row>
     <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1302,10 +1303,10 @@
     </row>
     <row r="7" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
@@ -1329,10 +1330,10 @@
     </row>
     <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>31</v>
@@ -1354,10 +1355,10 @@
     </row>
     <row r="9" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
